--- a/tract_geolocation_formatter/templates/farmer_group_master_data_template.xlsx
+++ b/tract_geolocation_formatter/templates/farmer_group_master_data_template.xlsx
@@ -962,7 +962,7 @@
     <t>version</t>
   </si>
   <si>
-    <t>Reference_ID</t>
+    <t>Node_ID</t>
   </si>
   <si>
     <t>Total_Cultivated_Area (ha)</t>
